--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D3C4E5-8F23-4661-83DC-AB09FE2553B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644C12A4-AA28-43A5-B846-565057FB3740}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="2" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -50,58 +50,58 @@
     <t>Title__c</t>
   </si>
   <si>
+    <t>StartDate__c</t>
+  </si>
+  <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>EndDate__c</t>
+  </si>
+  <si>
+    <t>Description__c</t>
+  </si>
+  <si>
+    <t>Automation Test Description</t>
+  </si>
+  <si>
+    <t>AccountSource__c</t>
+  </si>
+  <si>
+    <t>Automation Account</t>
+  </si>
+  <si>
+    <t>AgencyFund__c</t>
+  </si>
+  <si>
+    <t>Automation Fund</t>
+  </si>
+  <si>
+    <t>FiscalYear__c</t>
+  </si>
+  <si>
+    <t>SFY-21</t>
+  </si>
+  <si>
+    <t>AccountType__c</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>CostCategory__c</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>AppropriationBalance__c</t>
+  </si>
+  <si>
     <t>Automation Funding Source Regression</t>
   </si>
   <si>
-    <t>StartDate__c</t>
-  </si>
-  <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>EndDate__c</t>
-  </si>
-  <si>
     <t>Automation Funding Account Regression</t>
-  </si>
-  <si>
-    <t>Description__c</t>
-  </si>
-  <si>
-    <t>Automation Test Description</t>
-  </si>
-  <si>
-    <t>AccountSource__c</t>
-  </si>
-  <si>
-    <t>Automation Account</t>
-  </si>
-  <si>
-    <t>AgencyFund__c</t>
-  </si>
-  <si>
-    <t>Automation Fund</t>
-  </si>
-  <si>
-    <t>FiscalYear__c</t>
-  </si>
-  <si>
-    <t>SFY-21</t>
-  </si>
-  <si>
-    <t>AccountType__c</t>
-  </si>
-  <si>
-    <t>Revenue</t>
-  </si>
-  <si>
-    <t>CostCategory__c</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>AppropriationBalance__c</t>
   </si>
 </sst>
 </file>
@@ -485,7 +485,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -515,10 +515,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -526,10 +526,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
       </c>
       <c r="C3">
         <v>760</v>
@@ -546,7 +546,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -568,7 +568,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -576,10 +576,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -609,10 +609,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -620,10 +620,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
       </c>
       <c r="C3">
         <v>375</v>
@@ -631,65 +631,65 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9">
         <v>10000000</v>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644C12A4-AA28-43A5-B846-565057FB3740}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF45E929-E8E7-4C82-8237-5FD9BAB938F4}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="2" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -98,10 +98,10 @@
     <t>AppropriationBalance__c</t>
   </si>
   <si>
-    <t>Automation Funding Source Regression</t>
-  </si>
-  <si>
-    <t>Automation Funding Account Regression</t>
+    <t>Automation Funding Account</t>
+  </si>
+  <si>
+    <t>Automation Funding Source</t>
   </si>
 </sst>
 </file>
@@ -485,7 +485,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -568,7 +568,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF45E929-E8E7-4C82-8237-5FD9BAB938F4}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61F8975-DE9D-4093-B856-B92D75160746}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -459,14 +459,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -486,6 +486,28 @@
       </c>
       <c r="C2" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>760</v>
       </c>
     </row>
   </sheetData>
@@ -495,14 +517,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -513,26 +535,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
   </sheetData>
@@ -542,14 +553,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.33203125" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -560,7 +571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -571,7 +582,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -580,6 +591,17 @@
       </c>
       <c r="C3" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4">
+        <v>10000000</v>
       </c>
     </row>
   </sheetData>
@@ -589,14 +611,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.5546875" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -607,7 +629,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -618,7 +640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -629,7 +651,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -640,7 +662,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -651,7 +673,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -662,7 +684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -673,7 +695,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -682,17 +704,6 @@
       </c>
       <c r="C8" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9">
-        <v>10000000</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61F8975-DE9D-4093-B856-B92D75160746}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA079587-8567-45E7-854F-9C24AE657846}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -98,10 +98,10 @@
     <t>AppropriationBalance__c</t>
   </si>
   <si>
-    <t>Automation Funding Account</t>
-  </si>
-  <si>
-    <t>Automation Funding Source</t>
+    <t>Permanent Funding Source for Automation</t>
+  </si>
+  <si>
+    <t>Permanent Funding Account for Automation</t>
   </si>
 </sst>
 </file>
@@ -485,7 +485,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -512,6 +512,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -579,7 +580,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA079587-8567-45E7-854F-9C24AE657846}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25F76F1-63E4-4DBE-94DA-E55CA60DEB39}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="3612" yWindow="2448" windowWidth="17280" windowHeight="8964" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -98,10 +98,10 @@
     <t>AppropriationBalance__c</t>
   </si>
   <si>
-    <t>Permanent Funding Source for Automation</t>
-  </si>
-  <si>
     <t>Permanent Funding Account for Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Funding Source for Automation Testing</t>
   </si>
 </sst>
 </file>
@@ -460,13 +460,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -485,10 +485,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -499,7 +499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -519,13 +519,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -536,7 +536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -555,13 +555,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.28515625" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -572,7 +572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -580,10 +580,10 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -594,7 +594,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -613,13 +613,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -630,7 +630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -641,7 +641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -652,7 +652,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -663,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -674,7 +674,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -685,7 +685,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -696,7 +696,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25F76F1-63E4-4DBE-94DA-E55CA60DEB39}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1671B2AB-4BC4-47FC-829D-B899DC15A397}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3612" yWindow="2448" windowWidth="17280" windowHeight="8964" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -98,10 +98,10 @@
     <t>AppropriationBalance__c</t>
   </si>
   <si>
-    <t>Permanent Funding Account for Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Funding Source for Automation Testing</t>
+    <t>Automation Execution Funding Source</t>
+  </si>
+  <si>
+    <t>Automation Execution Funding Account</t>
   </si>
 </sst>
 </file>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -145,6 +145,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -460,13 +461,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -477,18 +478,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C2" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -499,7 +500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -519,13 +520,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -536,7 +537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -555,13 +556,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.33203125" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -572,18 +573,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C2" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -594,7 +595,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -613,13 +614,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.5546875" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -630,7 +631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -641,7 +642,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -652,7 +653,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -663,7 +664,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -674,7 +675,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -685,7 +686,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -696,7 +697,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1671B2AB-4BC4-47FC-829D-B899DC15A397}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CEFA49F-D8B2-4567-B1C0-18E5E0DB2F01}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -639,7 +639,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -650,7 +650,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>375</v>
+        <v>760</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CEFA49F-D8B2-4567-B1C0-18E5E0DB2F01}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E11638A-7DB6-4582-8270-FCEF1488350F}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21629"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E11638A-7DB6-4582-8270-FCEF1488350F}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201C5F30-F99D-4727-B373-BDC093C4451D}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -59,49 +59,49 @@
     <t>EndDate__c</t>
   </si>
   <si>
+    <t>AccountSource__c</t>
+  </si>
+  <si>
+    <t>Automation Account</t>
+  </si>
+  <si>
+    <t>AgencyFund__c</t>
+  </si>
+  <si>
+    <t>Automation Fund</t>
+  </si>
+  <si>
+    <t>FiscalYear__c</t>
+  </si>
+  <si>
+    <t>SFY-21</t>
+  </si>
+  <si>
+    <t>AccountType__c</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>CostCategory__c</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>AppropriationBalance__c</t>
+  </si>
+  <si>
+    <t>Automation Execution Funding Account</t>
+  </si>
+  <si>
+    <t>Funding Source Description</t>
+  </si>
+  <si>
     <t>Description__c</t>
   </si>
   <si>
-    <t>Automation Test Description</t>
-  </si>
-  <si>
-    <t>AccountSource__c</t>
-  </si>
-  <si>
-    <t>Automation Account</t>
-  </si>
-  <si>
-    <t>AgencyFund__c</t>
-  </si>
-  <si>
-    <t>Automation Fund</t>
-  </si>
-  <si>
-    <t>FiscalYear__c</t>
-  </si>
-  <si>
-    <t>SFY-21</t>
-  </si>
-  <si>
-    <t>AccountType__c</t>
-  </si>
-  <si>
-    <t>Revenue</t>
-  </si>
-  <si>
-    <t>CostCategory__c</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>AppropriationBalance__c</t>
-  </si>
-  <si>
     <t>Automation Execution Funding Source</t>
-  </si>
-  <si>
-    <t>Automation Execution Funding Account</t>
   </si>
 </sst>
 </file>
@@ -461,13 +461,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -478,7 +478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -486,29 +486,29 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
       <c r="C4">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
   </sheetData>
@@ -520,13 +520,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -537,7 +537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -556,13 +556,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.28515625" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,7 +573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -581,26 +581,26 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C4">
         <v>10000000</v>
@@ -608,19 +608,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -631,7 +632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -639,10 +640,10 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -650,62 +651,62 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201C5F30-F99D-4727-B373-BDC093C4451D}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7632C419-69F9-4CE7-9C65-50AFB3C33999}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -461,13 +461,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -478,7 +478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -489,7 +489,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -497,10 +497,10 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -520,13 +520,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -537,7 +537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -556,13 +556,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.33203125" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,7 +573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -584,7 +584,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -595,7 +595,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -615,13 +615,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.5546875" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,7 +632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -640,10 +640,10 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -651,10 +651,10 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -665,7 +665,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -676,7 +676,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -687,7 +687,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -698,7 +698,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21727"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7632C419-69F9-4CE7-9C65-50AFB3C33999}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B528B5-C65B-4FA7-B4DE-4B3B78655F60}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -497,7 +497,7 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -508,7 +508,7 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>761</v>
+        <v>3650</v>
       </c>
     </row>
   </sheetData>
@@ -640,7 +640,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -651,7 +651,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>750</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21901"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B528B5-C65B-4FA7-B4DE-4B3B78655F60}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC0EEAE-5438-4A50-BB9B-F1ADA47E7372}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -545,7 +545,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>761</v>
+        <v>3650</v>
       </c>
     </row>
   </sheetData>
@@ -640,7 +640,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\REI_Automation_Project\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC0EEAE-5438-4A50-BB9B-F1ADA47E7372}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B395C4-9344-40CA-A023-B51D3A9A22BD}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -461,13 +461,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -478,7 +478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -489,7 +489,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -500,7 +500,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -520,13 +520,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.69140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -537,7 +537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -556,13 +556,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.28515625" customWidth="1"/>
+    <col min="2" max="2" width="24.3828125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.3046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,7 +573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -584,7 +584,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -595,7 +595,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -615,13 +615,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,7 +632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -640,10 +640,10 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -654,7 +654,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -665,7 +665,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -676,7 +676,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -687,7 +687,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -698,7 +698,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\REI_Automation_Project\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B395C4-9344-40CA-A023-B51D3A9A22BD}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBA81BF-0A0C-4A77-8C3F-6A693A44CE13}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -461,13 +461,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -478,7 +478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -489,7 +489,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -500,7 +500,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -520,13 +520,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.69140625" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -537,7 +537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -556,13 +556,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.3046875" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,7 +573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -584,7 +584,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -595,7 +595,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -615,13 +615,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.53515625" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,7 +632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -643,7 +643,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -654,7 +654,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -665,7 +665,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -676,7 +676,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -687,7 +687,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -698,7 +698,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFBA81BF-0A0C-4A77-8C3F-6A693A44CE13}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B199B9-12E8-4D41-987F-794602D111EB}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="21">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -69,12 +69,6 @@
   </si>
   <si>
     <t>Automation Fund</t>
-  </si>
-  <si>
-    <t>FiscalYear__c</t>
-  </si>
-  <si>
-    <t>SFY-21</t>
   </si>
   <si>
     <t>AccountType__c</t>
@@ -486,7 +480,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -581,7 +575,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -589,10 +583,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -600,7 +594,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C4">
         <v>10000000</v>
@@ -614,7 +608,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
@@ -698,18 +692,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B199B9-12E8-4D41-987F-794602D111EB}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7F48DD-1451-4319-B17A-37F9BE5F471B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -574,7 +574,7 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>17</v>
       </c>
     </row>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7F48DD-1451-4319-B17A-37F9BE5F471B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112C2525-684A-4338-9BC5-7F5708B8373E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" activeTab="2" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -86,16 +86,16 @@
     <t>AppropriationBalance__c</t>
   </si>
   <si>
-    <t>Automation Execution Funding Account</t>
-  </si>
-  <si>
     <t>Funding Source Description</t>
   </si>
   <si>
     <t>Description__c</t>
   </si>
   <si>
-    <t>Automation Execution Funding Source</t>
+    <t>Automation Runtime Funding Source</t>
+  </si>
+  <si>
+    <t>Automation Runtime Funding Account</t>
   </si>
 </sst>
 </file>
@@ -455,13 +455,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -472,7 +472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -480,10 +480,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -494,7 +494,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -514,13 +514,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.69140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -550,13 +550,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.33203125" customWidth="1"/>
+    <col min="2" max="2" width="24.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.3046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -567,7 +567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -575,21 +575,21 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -609,13 +609,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.5546875" customWidth="1"/>
+    <col min="2" max="2" width="21.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -626,7 +626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -637,7 +637,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -648,7 +648,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -659,7 +659,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -670,7 +670,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -681,7 +681,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112C2525-684A-4338-9BC5-7F5708B8373E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A31296A4-8AB2-4817-944C-1C566CC81369}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" activeTab="2" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="23">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -96,19 +96,31 @@
   </si>
   <si>
     <t>Automation Runtime Funding Account</t>
+  </si>
+  <si>
+    <t>fieldEndDate__c</t>
+  </si>
+  <si>
+    <t>fieldStartDate__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="5"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -131,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -140,6 +152,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -455,13 +468,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -472,7 +485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -483,7 +496,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -494,7 +507,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -513,14 +526,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.69140625" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -531,32 +544,44 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
+      <c r="B2" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="C2">
         <v>3650</v>
       </c>
     </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="24.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.3046875" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -567,7 +592,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -578,7 +603,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -589,7 +614,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -609,13 +634,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="21.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.53515625" customWidth="1"/>
+    <col min="2" max="2" width="21.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -626,7 +651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -637,7 +662,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -648,7 +673,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -659,7 +684,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -670,7 +695,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -681,7 +706,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A31296A4-8AB2-4817-944C-1C566CC81369}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D382545-DDBF-4DC2-81A1-A312B19393C5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" activeTab="2" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="24">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -83,15 +83,9 @@
     <t>Construction</t>
   </si>
   <si>
-    <t>AppropriationBalance__c</t>
-  </si>
-  <si>
     <t>Funding Source Description</t>
   </si>
   <si>
-    <t>Description__c</t>
-  </si>
-  <si>
     <t>Automation Runtime Funding Source</t>
   </si>
   <si>
@@ -102,6 +96,15 @@
   </si>
   <si>
     <t>fieldStartDate__c</t>
+  </si>
+  <si>
+    <t>fieldTitle__c</t>
+  </si>
+  <si>
+    <t>fieldDescription__c</t>
+  </si>
+  <si>
+    <t>fieldAppropriationBalance__c</t>
   </si>
 </sst>
 </file>
@@ -493,7 +496,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
@@ -549,7 +552,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C2">
         <v>3650</v>
@@ -560,7 +563,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -597,10 +600,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
@@ -608,10 +611,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -619,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>10000000</v>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D382545-DDBF-4DC2-81A1-A312B19393C5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D322E2A1-F1C6-43F3-97EF-DAD818DFCA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" activeTab="2" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -471,13 +471,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F0A2B2E-B537-4457-8666-B87F52CC4438}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -488,7 +488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -499,7 +499,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -510,7 +510,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -530,13 +530,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{542C2F33-0CA3-46B6-B0DA-5252E99270E2}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -547,7 +547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -558,7 +558,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -578,13 +578,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8F565D-4A1E-40DC-8370-113D6BE62705}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.33203125" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="51.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -595,37 +595,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+      <c r="C3">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4">
-        <v>10000000</v>
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -637,13 +637,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F784967-C83D-450C-97CE-71BB91D2ED97}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.53125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -654,7 +654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -665,7 +665,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -676,7 +676,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -687,7 +687,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -698,7 +698,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -709,7 +709,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D322E2A1-F1C6-43F3-97EF-DAD818DFCA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FA02EE-FCC3-450A-B733-1ACDAE7F4A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -59,27 +59,15 @@
     <t>EndDate__c</t>
   </si>
   <si>
-    <t>AccountSource__c</t>
-  </si>
-  <si>
     <t>Automation Account</t>
   </si>
   <si>
-    <t>AgencyFund__c</t>
-  </si>
-  <si>
     <t>Automation Fund</t>
   </si>
   <si>
-    <t>AccountType__c</t>
-  </si>
-  <si>
     <t>Revenue</t>
   </si>
   <si>
-    <t>CostCategory__c</t>
-  </si>
-  <si>
     <t>Construction</t>
   </si>
   <si>
@@ -105,13 +93,25 @@
   </si>
   <si>
     <t>fieldAppropriationBalance__c</t>
+  </si>
+  <si>
+    <t>fieldAccountSource__c</t>
+  </si>
+  <si>
+    <t>fieldAgencyFund__c</t>
+  </si>
+  <si>
+    <t>fieldAccountType__c</t>
+  </si>
+  <si>
+    <t>fieldCostCategory__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,6 +122,12 @@
     <font>
       <sz val="5"/>
       <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF202124"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -146,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -156,6 +162,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -496,7 +503,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -552,7 +559,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>3650</v>
@@ -563,7 +570,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -600,10 +607,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -611,7 +618,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C3">
         <v>10000000</v>
@@ -622,10 +629,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -658,8 +665,8 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
+      <c r="B2" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -669,8 +676,8 @@
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
+      <c r="B3" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C3">
         <v>2650</v>
@@ -680,44 +687,44 @@
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
+      <c r="B5" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s">
-        <v>12</v>
+      <c r="B6" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>14</v>
+      <c r="B7" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/FundingSource_Field_Values.xlsx
+++ b/src/main/resources/FundingSource_Field_Values.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FA02EE-FCC3-450A-B733-1ACDAE7F4A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0B36C0-C33E-4941-B8F4-FA9D379E4EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="4" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
     <sheet name="Edition" sheetId="2" r:id="rId2"/>
     <sheet name="Funding Account Creation" sheetId="3" r:id="rId3"/>
     <sheet name="Funding Account Edition" sheetId="4" r:id="rId4"/>
+    <sheet name="External_fs_Creation" sheetId="5" r:id="rId5"/>
+    <sheet name="External_FS_Edition" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet4" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="29">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -105,13 +108,28 @@
   </si>
   <si>
     <t>fieldCostCategory__c</t>
+  </si>
+  <si>
+    <t>fieldGrant__c</t>
+  </si>
+  <si>
+    <t>Poonam17420</t>
+  </si>
+  <si>
+    <t>Automation Runtime External Funding Source</t>
+  </si>
+  <si>
+    <t>fieldType__c</t>
+  </si>
+  <si>
+    <t>Federal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,16 +149,27 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Helvetica"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E8E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -148,11 +177,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -163,6 +207,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -731,4 +778,117 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDBC494-3495-4593-8893-281AC781034C}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75053FB5-B5D7-4C03-8DB8-0079B98D3AB8}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04E97906-8EED-4E90-A72C-6528249228F5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>